--- a/artfynd/A 587-2024 artfynd.xlsx
+++ b/artfynd/A 587-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118834796</v>
+        <v>118833408</v>
       </c>
       <c r="B2" t="n">
-        <v>57306</v>
+        <v>57718</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Anstorp, Nrk</t>
+          <t>Sofielund, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532731</v>
+        <v>532743</v>
       </c>
       <c r="R2" t="n">
-        <v>6547793</v>
+        <v>6548078</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118833408</v>
+        <v>118834796</v>
       </c>
       <c r="B3" t="n">
-        <v>57718</v>
+        <v>57306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,41 +811,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sofielund, Nrk</t>
+          <t>Anstorp, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532743</v>
+        <v>532731</v>
       </c>
       <c r="R3" t="n">
-        <v>6548078</v>
+        <v>6547793</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 587-2024 artfynd.xlsx
+++ b/artfynd/A 587-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118833408</v>
+        <v>118834796</v>
       </c>
       <c r="B2" t="n">
-        <v>57718</v>
+        <v>57306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,41 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sofielund, Nrk</t>
+          <t>Anstorp, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532743</v>
+        <v>532731</v>
       </c>
       <c r="R2" t="n">
-        <v>6548078</v>
+        <v>6547793</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -795,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118834796</v>
+        <v>118833408</v>
       </c>
       <c r="B3" t="n">
-        <v>57306</v>
+        <v>57718</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,46 +816,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Anstorp, Nrk</t>
+          <t>Sofielund, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532731</v>
+        <v>532743</v>
       </c>
       <c r="R3" t="n">
-        <v>6547793</v>
+        <v>6548078</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
